--- a/artfynd/A 49680-2022 artfynd.xlsx
+++ b/artfynd/A 49680-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49680-2022 artfynd.xlsx
+++ b/artfynd/A 49680-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>92331751</v>
       </c>
       <c r="B2" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633236.1484752755</v>
+        <v>633236</v>
       </c>
       <c r="R2" t="n">
-        <v>6563992.220321954</v>
+        <v>6563992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2021-04-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-04-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92331911</v>
+        <v>92331788</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633218.7539394327</v>
+        <v>633224</v>
       </c>
       <c r="R3" t="n">
-        <v>6564004.942372089</v>
+        <v>6564004</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,24 +853,14 @@
           <t>2021-04-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grenar på gammal döende gran.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,127 +885,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>92331788</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Micklaberg, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>633223.9196854326</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6564004.097652578</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Nykvarn</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Taxinge</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-04-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-04-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49680-2022 artfynd.xlsx
+++ b/artfynd/A 49680-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92331788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92331751</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>